--- a/links/Juegos_PSP.xlsx
+++ b/links/Juegos_PSP.xlsx
@@ -397,14 +397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:R21"/>
   <cols>
     <col min="1" max="1" width="45.83203125" customWidth="1"/>
     <col min="2" max="2" width="45.83203125" customWidth="1"/>
     <col min="3" max="3" width="45.83203125" customWidth="1"/>
     <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="35.83203125" customWidth="1"/>
+    <col min="5" max="5" width="50.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
     <col min="7" max="7" width="35.83203125" customWidth="1"/>
     <col min="8" max="8" width="35.83203125" customWidth="1"/>
     <col min="9" max="9" width="35.83203125" customWidth="1"/>
@@ -417,9 +417,6 @@
     <col min="16" max="16" width="35.83203125" customWidth="1"/>
     <col min="17" max="17" width="35.83203125" customWidth="1"/>
     <col min="18" max="18" width="35.83203125" customWidth="1"/>
-    <col min="19" max="19" width="35.83203125" customWidth="1"/>
-    <col min="20" max="20" width="35.83203125" customWidth="1"/>
-    <col min="21" max="21" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -436,54 +433,45 @@
         <v>Imagen Local</v>
       </c>
       <c r="E1" t="str">
+        <v>Sinopsis</v>
+      </c>
+      <c r="F1" t="str">
         <v>En Varias Partes</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Mega</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Mediafire</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>1Fichier</v>
       </c>
-      <c r="I1" t="str">
-        <v>1Fichier Parte 1</v>
-      </c>
       <c r="J1" t="str">
-        <v>1Fichier Parte 2</v>
+        <v>Google Drive</v>
       </c>
       <c r="K1" t="str">
-        <v>1Fichier Parte 3</v>
+        <v>Qiwi</v>
       </c>
       <c r="L1" t="str">
-        <v>1Fichier Parte 4</v>
+        <v>Pixeldrain</v>
       </c>
       <c r="M1" t="str">
-        <v>Google Drive</v>
+        <v>Megaup</v>
       </c>
       <c r="N1" t="str">
-        <v>Qiwi</v>
+        <v>Otro Link 1</v>
       </c>
       <c r="O1" t="str">
-        <v>Pixeldrain</v>
+        <v>Otro Link 2</v>
       </c>
       <c r="P1" t="str">
-        <v>Megaup</v>
+        <v>Otro Link 3</v>
       </c>
       <c r="Q1" t="str">
-        <v>Otro Link 1</v>
+        <v>Otro Link 4</v>
       </c>
       <c r="R1" t="str">
-        <v>Otro Link 2</v>
-      </c>
-      <c r="S1" t="str">
-        <v>Otro Link 3</v>
-      </c>
-      <c r="T1" t="str">
-        <v>Otro Link 4</v>
-      </c>
-      <c r="U1" t="str">
         <v>Otro Link 5</v>
       </c>
     </row>
@@ -501,27 +489,30 @@
         <v>imagenes/PSP/Dragon Ball Z Shin Budokai Another Road.jpg</v>
       </c>
       <c r="E2" t="str">
-        <v>No</v>
-      </c>
-      <c r="H2" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F2" t="str">
+        <v>No</v>
+      </c>
+      <c r="I2" t="str">
         <v>https://1fichier.com/?mv03mz5l6n0ywwby1coe</v>
       </c>
-      <c r="M2" t="str">
+      <c r="J2" t="str">
         <v>https://gamepciso.com/guide-fix-error-limit-download-google-drive/: https://gamepciso.com/guide-fix-error-limit-download-google-drive/</v>
       </c>
+      <c r="N2" t="str">
+        <v>https://docs.google.com/uc?id=0B3Xk5Pcz2KrcSllMLXZ0LTZRblU&amp;export=download</v>
+      </c>
+      <c r="O2" t="str">
+        <v>http://download.freeroms.com/psp_roms/popular/dragon_ball_z_-_shin_budokai_-_another_road.zip</v>
+      </c>
+      <c r="P2" t="str">
+        <v>http://download.freeroms.com/psp_roms/d/dragon_ball_z_-_shin_budokai_-_another_road_(europe).zip</v>
+      </c>
       <c r="Q2" t="str">
-        <v>https://docs.google.com/uc?id=0B3Xk5Pcz2KrcSllMLXZ0LTZRblU&amp;export=download</v>
+        <v>https://downloadgamepsp.org/guide-download-game/: https://downloadgamepsp.org/guide-download-game/</v>
       </c>
       <c r="R2" t="str">
-        <v>http://download.freeroms.com/psp_roms/popular/dragon_ball_z_-_shin_budokai_-_another_road.zip</v>
-      </c>
-      <c r="S2" t="str">
-        <v>http://download.freeroms.com/psp_roms/d/dragon_ball_z_-_shin_budokai_-_another_road_(europe).zip</v>
-      </c>
-      <c r="T2" t="str">
-        <v>https://downloadgamepsp.org/guide-download-game/: https://downloadgamepsp.org/guide-download-game/</v>
-      </c>
-      <c r="U2" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -539,24 +530,18 @@
         <v>imagenes/PSP/God of War Chains of Olympus.jpg</v>
       </c>
       <c r="E3" t="str">
-        <v>No</v>
-      </c>
-      <c r="I3" t="str">
-        <v>https://1fichier.com/?oxgrxlobxqfczta1ej2b</v>
-      </c>
-      <c r="J3" t="str">
-        <v>https://1fichier.com/?bm0n5pnscf5v8ppnh29p</v>
-      </c>
-      <c r="K3" t="str">
-        <v>https://1fichier.com/?s2k4blyxq90xyx5z2hc0</v>
-      </c>
-      <c r="Q3" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F3" t="str">
+        <v>No</v>
+      </c>
+      <c r="N3" t="str">
         <v>http://download.freeroms.com/psp_roms/popular/god_of_war_-_chains_of_olympus_(europe).zip</v>
       </c>
-      <c r="R3" t="str">
+      <c r="O3" t="str">
         <v>https://downloadgamepsp.org/god-of-war-chains-of-olympus-psp-ppsspp-psvita-full-iso/: https://downloadgamepsp.org/god-of-war-chains-of-olympus-psp-ppsspp-psvita-full-iso/</v>
       </c>
-      <c r="S3" t="str">
+      <c r="P3" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -574,21 +559,18 @@
         <v>imagenes/PSP/Naruto Shippuden Legends Akatsuki Rising.jpg</v>
       </c>
       <c r="E4" t="str">
-        <v>No</v>
-      </c>
-      <c r="I4" t="str">
-        <v>https://1fichier.com/?nblqsf1i4hrgbjrogx5i</v>
-      </c>
-      <c r="J4" t="str">
-        <v>https://1fichier.com/?76nkyzbb6l79zguesb0u</v>
-      </c>
-      <c r="Q4" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F4" t="str">
+        <v>No</v>
+      </c>
+      <c r="N4" t="str">
         <v>http://download.freeroms.com/psp_roms/n/naruto_shippuden_-_legends_-_akatsuki_rising_(europe).zip</v>
       </c>
-      <c r="R4" t="str">
+      <c r="O4" t="str">
         <v>http://download.freeroms.com/psp_roms/popular/naruto_shippuden_-_legends_-_akatsuki_rising.zip</v>
       </c>
-      <c r="S4" t="str">
+      <c r="P4" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -606,27 +588,21 @@
         <v>imagenes/PSP/Naruto Shippuden Ultimate Ninja Heroes 3.jpg</v>
       </c>
       <c r="E5" t="str">
-        <v>No</v>
-      </c>
-      <c r="I5" t="str">
-        <v>https://1fichier.com/?6whaaewgc1qqd1c3w0js</v>
-      </c>
-      <c r="J5" t="str">
-        <v>https://1fichier.com/?07t101d465li0au5iasb</v>
-      </c>
-      <c r="K5" t="str">
-        <v>https://1fichier.com/?3fpgtwpx2lth4a8uvu3p</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F5" t="str">
+        <v>No</v>
+      </c>
+      <c r="N5" t="str">
+        <v>http://download.freeroms.com/psp_roms/popular/naruto_shippuden_-_ultimate_ninja_heroes_3.zip</v>
+      </c>
+      <c r="O5" t="str">
+        <v>http://download.freeroms.com/psp_roms/popular/naruto_shippuden_-_ultimate_ninja_heroes_3_(europe).zip</v>
+      </c>
+      <c r="P5" t="str">
+        <v>https://downloadgamepsp.org/guide-download-game/: https://downloadgamepsp.org/guide-download-game/</v>
       </c>
       <c r="Q5" t="str">
-        <v>http://download.freeroms.com/psp_roms/popular/naruto_shippuden_-_ultimate_ninja_heroes_3.zip</v>
-      </c>
-      <c r="R5" t="str">
-        <v>http://download.freeroms.com/psp_roms/popular/naruto_shippuden_-_ultimate_ninja_heroes_3_(europe).zip</v>
-      </c>
-      <c r="S5" t="str">
-        <v>https://downloadgamepsp.org/guide-download-game/: https://downloadgamepsp.org/guide-download-game/</v>
-      </c>
-      <c r="T5" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -644,27 +620,21 @@
         <v>imagenes/PSP/Dragon Ball Z Shin Budokai.jpg</v>
       </c>
       <c r="E6" t="str">
-        <v>No</v>
-      </c>
-      <c r="I6" t="str">
-        <v>https://1fichier.com/?t5u8mlrovlfdxbg4y10o</v>
-      </c>
-      <c r="J6" t="str">
-        <v>https://1fichier.com/?94yzy0ctss86j6lbpyna</v>
-      </c>
-      <c r="K6" t="str">
-        <v>https://1fichier.com/?e390hubbr9ju3oj51s1x</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F6" t="str">
+        <v>No</v>
+      </c>
+      <c r="N6" t="str">
+        <v>http://download.freeroms.com/psp_roms/popular/dragon_ball_z_-_shin_budokai_(europe).zip</v>
+      </c>
+      <c r="O6" t="str">
+        <v>http://download.freeroms.com/psp_roms/popular/dragon_ball_z_-_shin_budokai.zip</v>
+      </c>
+      <c r="P6" t="str">
+        <v>http://download.freeroms.com/psp_roms/d/dragon_ball_z_-_shin_budokai_(japan).zip</v>
       </c>
       <c r="Q6" t="str">
-        <v>http://download.freeroms.com/psp_roms/popular/dragon_ball_z_-_shin_budokai_(europe).zip</v>
-      </c>
-      <c r="R6" t="str">
-        <v>http://download.freeroms.com/psp_roms/popular/dragon_ball_z_-_shin_budokai.zip</v>
-      </c>
-      <c r="S6" t="str">
-        <v>http://download.freeroms.com/psp_roms/d/dragon_ball_z_-_shin_budokai_(japan).zip</v>
-      </c>
-      <c r="T6" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -682,30 +652,24 @@
         <v>imagenes/PSP/Naruto Shippuden Ultimate Ninja Impact.jpg</v>
       </c>
       <c r="E7" t="str">
-        <v>No</v>
-      </c>
-      <c r="I7" t="str">
-        <v>https://1fichier.com/?y82kste1svf8zjf10i0l</v>
-      </c>
-      <c r="J7" t="str">
-        <v>https://1fichier.com/?sexdxekzaax89637q6mo</v>
-      </c>
-      <c r="K7" t="str">
-        <v>https://1fichier.com/?qh7fwdezje6cm5fqo06t</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F7" t="str">
+        <v>No</v>
+      </c>
+      <c r="N7" t="str">
+        <v>http://download.freeroms.com/psp_roms/popular/naruto_shippuden_-_ultimate_ninja_impact.zip</v>
+      </c>
+      <c r="O7" t="str">
+        <v>http://download.freeroms.com/psp_roms/popular/naruto_shippuden_-_ultimate_ninja_impact_(europe).zip</v>
+      </c>
+      <c r="P7" t="str">
+        <v>https://filecrypt.cc/Container/91F43681AB.html</v>
       </c>
       <c r="Q7" t="str">
-        <v>http://download.freeroms.com/psp_roms/popular/naruto_shippuden_-_ultimate_ninja_impact.zip</v>
+        <v>https://downloadgamepsp.org/guide-download-game/: https://downloadgamepsp.org/guide-download-game/</v>
       </c>
       <c r="R7" t="str">
-        <v>http://download.freeroms.com/psp_roms/popular/naruto_shippuden_-_ultimate_ninja_impact_(europe).zip</v>
-      </c>
-      <c r="S7" t="str">
-        <v>https://filecrypt.cc/Container/91F43681AB.html</v>
-      </c>
-      <c r="T7" t="str">
-        <v>https://downloadgamepsp.org/guide-download-game/: https://downloadgamepsp.org/guide-download-game/</v>
-      </c>
-      <c r="U7" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -723,18 +687,15 @@
         <v>imagenes/PSP/Dragon Ball Z Tenkaichi Tag Team.jpg</v>
       </c>
       <c r="E8" t="str">
-        <v>No</v>
-      </c>
-      <c r="I8" t="str">
-        <v>https://1fichier.com/?va8w4f10qgemgjjl013j</v>
-      </c>
-      <c r="J8" t="str">
-        <v>https://1fichier.com/?h62hd8ia7jm6hku3pdie</v>
-      </c>
-      <c r="Q8" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F8" t="str">
+        <v>No</v>
+      </c>
+      <c r="N8" t="str">
         <v>https://downloadgamepsp.org/guide-download-game/: https://downloadgamepsp.org/guide-download-game/</v>
       </c>
-      <c r="R8" t="str">
+      <c r="O8" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -752,18 +713,21 @@
         <v>imagenes/PSP/SD Gundam G Generation World.jpg</v>
       </c>
       <c r="E9" t="str">
-        <v>No</v>
-      </c>
-      <c r="H9" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F9" t="str">
+        <v>No</v>
+      </c>
+      <c r="I9" t="str">
         <v>https://1fichier.com/?4sn19tpn20z54kdi1jk4</v>
       </c>
-      <c r="M9" t="str">
+      <c r="J9" t="str">
         <v>https://drive.google.com/uc?id=0BxkjDKoHyq8GRFo1Z2R1ZkFSV2M&amp;export=download</v>
       </c>
-      <c r="Q9" t="str">
+      <c r="N9" t="str">
         <v>http://download.freeroms.com/psp_roms/s/sd_gundam_g_generation_world_japan.zip</v>
       </c>
-      <c r="R9" t="str">
+      <c r="O9" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -781,12 +745,15 @@
         <v>imagenes/PSP/WWE Smackdown Vs Raw 2K14.jpg</v>
       </c>
       <c r="E10" t="str">
-        <v>No</v>
-      </c>
-      <c r="M10" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F10" t="str">
+        <v>No</v>
+      </c>
+      <c r="J10" t="str">
         <v>https://drive.google.com/uc?id=0B9foslseMN79eGMwMl9IVW9lVVk&amp;export=download</v>
       </c>
-      <c r="Q10" t="str">
+      <c r="N10" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -804,27 +771,21 @@
         <v>imagenes/PSP/SoulCalibur Broken Destiny.jpg</v>
       </c>
       <c r="E11" t="str">
-        <v>No</v>
-      </c>
-      <c r="I11" t="str">
-        <v>https://1fichier.com/?s1f2hfeya5et4pceuwn7</v>
-      </c>
-      <c r="J11" t="str">
-        <v>https://1fichier.com/?iknstjsc2apzssk2dui2</v>
-      </c>
-      <c r="K11" t="str">
-        <v>https://1fichier.com/?x7ft5b1hh19kkjaqdhw2</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F11" t="str">
+        <v>No</v>
+      </c>
+      <c r="N11" t="str">
+        <v>http://download.freeroms.com/psp_roms/popular/soul_calibur_-_broken_destiny.zip</v>
+      </c>
+      <c r="O11" t="str">
+        <v>http://download.freeroms.com/psp_roms/s/soul_calibur_-_broken_destiny_europe_(m6).zip</v>
+      </c>
+      <c r="P11" t="str">
+        <v>http://download.freeroms.com/psp_roms/s/soul_calibur_-_broken_destiny_japan.zip</v>
       </c>
       <c r="Q11" t="str">
-        <v>http://download.freeroms.com/psp_roms/popular/soul_calibur_-_broken_destiny.zip</v>
-      </c>
-      <c r="R11" t="str">
-        <v>http://download.freeroms.com/psp_roms/s/soul_calibur_-_broken_destiny_europe_(m6).zip</v>
-      </c>
-      <c r="S11" t="str">
-        <v>http://download.freeroms.com/psp_roms/s/soul_calibur_-_broken_destiny_japan.zip</v>
-      </c>
-      <c r="T11" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -842,21 +803,12 @@
         <v>imagenes/PSP/Pro Evolution Soccer 2014 [PES 2014].jpg</v>
       </c>
       <c r="E12" t="str">
-        <v>No</v>
-      </c>
-      <c r="I12" t="str">
-        <v>https://1fichier.com/?d2y0362zl7b78kbx8bfo</v>
-      </c>
-      <c r="J12" t="str">
-        <v>https://1fichier.com/?grns8ey2h298pdoy91qz</v>
-      </c>
-      <c r="K12" t="str">
-        <v>https://1fichier.com/?exofk2au1hr4awfgmp1v</v>
-      </c>
-      <c r="L12" t="str">
-        <v>https://1fichier.com/?mwbc9xh8rrw5ffu0xp0e</v>
-      </c>
-      <c r="Q12" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F12" t="str">
+        <v>No</v>
+      </c>
+      <c r="N12" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -874,24 +826,21 @@
         <v>imagenes/PSP/Ys Seven.jpg</v>
       </c>
       <c r="E13" t="str">
-        <v>No</v>
-      </c>
-      <c r="I13" t="str">
-        <v>https://1fichier.com/?tx7lbkmhjrw5aw21wpno</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F13" t="str">
+        <v>No</v>
       </c>
       <c r="J13" t="str">
-        <v>https://1fichier.com/?iq3dztxm3j7clb1nltow</v>
-      </c>
-      <c r="M13" t="str">
         <v>https://drive.google.com/uc?id=0B3eHeWAhGw5TU0VPZ0NsSHpLRXc&amp;export=download%20target=_blank</v>
       </c>
-      <c r="Q13" t="str">
+      <c r="N13" t="str">
         <v>http://download.freeroms.com/psp_roms/y/ys_seven.zip</v>
       </c>
-      <c r="R13" t="str">
+      <c r="O13" t="str">
         <v>http://download.freeroms.com/psp_roms/y/ys_seven_japan.zip</v>
       </c>
-      <c r="S13" t="str">
+      <c r="P13" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -909,21 +858,18 @@
         <v>imagenes/PSP/Def Jam Fight For NY The Takeover.jpg</v>
       </c>
       <c r="E14" t="str">
-        <v>No</v>
-      </c>
-      <c r="I14" t="str">
-        <v>https://1fichier.com/?8jermzrairrv6f3g5dp8</v>
-      </c>
-      <c r="J14" t="str">
-        <v>https://1fichier.com/?ezcayyf9r3x8ho24rehz</v>
-      </c>
-      <c r="Q14" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F14" t="str">
+        <v>No</v>
+      </c>
+      <c r="N14" t="str">
         <v>http://download.freeroms.com/psp_roms/d/def_jam_-_fight_for_ny_-_the_takeover_(europe).zip</v>
       </c>
-      <c r="R14" t="str">
+      <c r="O14" t="str">
         <v>http://download.freeroms.com/psp_roms/popular/def_jam_-_fight_for_ny_-_the_takeover.zip</v>
       </c>
-      <c r="S14" t="str">
+      <c r="P14" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -941,27 +887,21 @@
         <v>imagenes/PSP/Dissidia Final Fantasy.jpg</v>
       </c>
       <c r="E15" t="str">
-        <v>No</v>
-      </c>
-      <c r="I15" t="str">
-        <v>https://1fichier.com/?fkmx658kc5kwes218lxz</v>
-      </c>
-      <c r="J15" t="str">
-        <v>https://1fichier.com/?7b3lcxq406tf5462yarh</v>
-      </c>
-      <c r="K15" t="str">
-        <v>https://1fichier.com/?m4a07sazkcwwrrdb9pma</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F15" t="str">
+        <v>No</v>
+      </c>
+      <c r="N15" t="str">
+        <v>http://download.freeroms.com/psp_roms/d/dissidia_-_final_fantasy_(europe).zip</v>
+      </c>
+      <c r="O15" t="str">
+        <v>http://download.freeroms.com/psp_roms/d/dissidia_-_final_fantasy.zip</v>
+      </c>
+      <c r="P15" t="str">
+        <v>http://download.freeroms.com/psp_roms/d/dissidia_-_final_fantasy_(japan).zip</v>
       </c>
       <c r="Q15" t="str">
-        <v>http://download.freeroms.com/psp_roms/d/dissidia_-_final_fantasy_(europe).zip</v>
-      </c>
-      <c r="R15" t="str">
-        <v>http://download.freeroms.com/psp_roms/d/dissidia_-_final_fantasy.zip</v>
-      </c>
-      <c r="S15" t="str">
-        <v>http://download.freeroms.com/psp_roms/d/dissidia_-_final_fantasy_(japan).zip</v>
-      </c>
-      <c r="T15" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -979,21 +919,18 @@
         <v>imagenes/PSP/Worms Open Warfare 2.jpg</v>
       </c>
       <c r="E16" t="str">
-        <v>No</v>
-      </c>
-      <c r="I16" t="str">
-        <v>https://1fichier.com/?vz8cruqtgw2kp8gqra3u</v>
-      </c>
-      <c r="J16" t="str">
-        <v>https://1fichier.com/?l894jk6kp3qeojmzaxyl</v>
-      </c>
-      <c r="Q16" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F16" t="str">
+        <v>No</v>
+      </c>
+      <c r="N16" t="str">
         <v>http://download.freeroms.com/psp_roms/w/worms_-_open_warfare_2.zip</v>
       </c>
-      <c r="R16" t="str">
+      <c r="O16" t="str">
         <v>http://download.freeroms.com/psp_roms/w/worms_-_open_warfare_2_europe_(m5).zip</v>
       </c>
-      <c r="S16" t="str">
+      <c r="P16" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1011,21 +948,18 @@
         <v>imagenes/PSP/Rock Band Unplugged.jpg</v>
       </c>
       <c r="E17" t="str">
-        <v>No</v>
-      </c>
-      <c r="I17" t="str">
-        <v>https://1fichier.com/?ws9m4smxpyh2hbgelsgg</v>
-      </c>
-      <c r="J17" t="str">
-        <v>https://1fichier.com/?6hjcovd0omyh34q10coi</v>
-      </c>
-      <c r="Q17" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F17" t="str">
+        <v>No</v>
+      </c>
+      <c r="N17" t="str">
         <v>http://download.freeroms.com/psp_roms/r/rock_band_unplugged.zip</v>
       </c>
-      <c r="R17" t="str">
+      <c r="O17" t="str">
         <v>http://download.freeroms.com/psp_roms/r/rock_band_unplugged_europe_(m5).zip</v>
       </c>
-      <c r="S17" t="str">
+      <c r="P17" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1043,24 +977,21 @@
         <v>imagenes/PSP/The Warriors.jpg</v>
       </c>
       <c r="E18" t="str">
-        <v>No</v>
-      </c>
-      <c r="I18" t="str">
-        <v>https://1fichier.com/?4w2h6hj7sivg693ausg5</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F18" t="str">
+        <v>No</v>
       </c>
       <c r="J18" t="str">
-        <v>https://1fichier.com/?sh1bwdr377tovn8jhdbr</v>
-      </c>
-      <c r="M18" t="str">
         <v>https://drive.google.com/uc?id=0B3eHeWAhGw5TX2pZLUJVSVJLWlU&amp;export=download%20target=_blank</v>
       </c>
-      <c r="Q18" t="str">
+      <c r="N18" t="str">
         <v>http://download.freeroms.com/psp_roms/w/warriors,_the_europe.zip</v>
       </c>
-      <c r="R18" t="str">
+      <c r="O18" t="str">
         <v>http://download.freeroms.com/psp_roms/w/warriors,_the.zip</v>
       </c>
-      <c r="S18" t="str">
+      <c r="P18" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1078,18 +1009,21 @@
         <v>imagenes/PSP/Kidou Senshi Gundam AGE Cosmic Drive [English Patc.jpg</v>
       </c>
       <c r="E19" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F19" t="str">
+        <v>No</v>
+      </c>
+      <c r="G19" t="str">
         <v>https://filecrypt.cc/Container/B48BA6E564.html</v>
       </c>
-      <c r="H19" t="str">
+      <c r="I19" t="str">
         <v>https://1fichier.com/?3rt7r3azeqjvd4q4zj0u</v>
       </c>
-      <c r="M19" t="str">
+      <c r="J19" t="str">
         <v>http://download.freeroms.com/psp_roms/k/kidou_senshi_gundam_age_-_cosmic_drive_(japan).zip</v>
       </c>
-      <c r="Q19" t="str">
+      <c r="N19" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1107,27 +1041,21 @@
         <v>imagenes/PSP/Valkyrie Profile Lenneth.jpg</v>
       </c>
       <c r="E20" t="str">
-        <v>No</v>
-      </c>
-      <c r="I20" t="str">
-        <v>https://1fichier.com/?e76lzkj1q4pybpuownrd</v>
-      </c>
-      <c r="J20" t="str">
-        <v>https://1fichier.com/?bhwjpdcnvxibevrbcv86</v>
-      </c>
-      <c r="K20" t="str">
-        <v>https://1fichier.com/?r9eabqkj5chwe6l9puuz</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F20" t="str">
+        <v>No</v>
+      </c>
+      <c r="N20" t="str">
+        <v>http://download.freeroms.com/psp_roms/v/valkyrie_profile_-_lenneth.zip</v>
+      </c>
+      <c r="O20" t="str">
+        <v>http://download.freeroms.com/psp_roms/v/valkyrie_profile_-_lenneth_europe.zip</v>
+      </c>
+      <c r="P20" t="str">
+        <v>http://download.freeroms.com/psp_roms/v/valkyrie_profile_-_lenneth_japan.zip</v>
       </c>
       <c r="Q20" t="str">
-        <v>http://download.freeroms.com/psp_roms/v/valkyrie_profile_-_lenneth.zip</v>
-      </c>
-      <c r="R20" t="str">
-        <v>http://download.freeroms.com/psp_roms/v/valkyrie_profile_-_lenneth_europe.zip</v>
-      </c>
-      <c r="S20" t="str">
-        <v>http://download.freeroms.com/psp_roms/v/valkyrie_profile_-_lenneth_japan.zip</v>
-      </c>
-      <c r="T20" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1145,24 +1073,27 @@
         <v>imagenes/PSP/Hot Shots Tennis Get A Grip.jpg</v>
       </c>
       <c r="E21" t="str">
-        <v>No</v>
-      </c>
-      <c r="H21" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F21" t="str">
+        <v>No</v>
+      </c>
+      <c r="I21" t="str">
         <v>https://1fichier.com/?0c8m8g7vsvpdmtzah7ie</v>
       </c>
-      <c r="M21" t="str">
+      <c r="J21" t="str">
         <v>https://drive.google.com/uc?id=0BygSYj4HJSoFN3R5TmdSYlpPXzg&amp;export=download%20target=_blank</v>
       </c>
-      <c r="Q21" t="str">
+      <c r="N21" t="str">
         <v>http://download.freeroms.com/psp_roms/h/hot_shots_tennis_-_get_a_grip_(usa).zip</v>
       </c>
-      <c r="R21" t="str">
+      <c r="O21" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R21"/>
   </ignoredErrors>
 </worksheet>
 </file>